--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9946-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9946-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBF506E6-66C9-4CC0-90CE-532C67F2027C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D28881C-B3E1-4F51-8B6B-FA96BB8C1FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A7A6277C-C568-40E3-AE61-18A38B626C74}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B57EF2C2-441C-4B23-915B-6DC2EDFB03DB}"/>
   </bookViews>
   <sheets>
     <sheet name="9946-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1490,28 +1490,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D08CB4-9655-4DAF-B9FC-64117AD9ED9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47EE949C-6238-43CB-B07B-B507F230C1C0}">
   <dimension ref="A1:X39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1701,7 +1701,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2023</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2022</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2021</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2020</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2019</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2018</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>8.26</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2017</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2016</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2015</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2014</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2013</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2012</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2011</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2010</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2009</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2008</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2007</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2006</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2005</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2004</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2003</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2002</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2001</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2000</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>1999</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1998</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
         <v>51</v>
       </c>
